--- a/artfynd/A 42239-2021 artfynd.xlsx
+++ b/artfynd/A 42239-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42239-2021 artfynd.xlsx
+++ b/artfynd/A 42239-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53973876</v>
+        <v>53973874</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564748.7709642444</v>
+        <v>564607</v>
       </c>
       <c r="R2" t="n">
-        <v>7113434.260610383</v>
+        <v>7113373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-06-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +764,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -792,7 +777,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # Salix caprea</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,15 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53973874</v>
+        <v>53973875</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -854,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564606.6153696453</v>
+        <v>564607</v>
       </c>
       <c r="R3" t="n">
-        <v>7113373.207906861</v>
+        <v>7113373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,19 +867,9 @@
           <t>2015-06-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-06-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,12 +888,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -931,7 +901,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -953,15 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53973875</v>
+        <v>53973876</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564606.6153696453</v>
+        <v>564749</v>
       </c>
       <c r="R4" t="n">
-        <v>7113373.207906861</v>
+        <v>7113434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,19 +991,9 @@
           <t>2015-06-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1057,12 +1012,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1070,7 +1025,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # Populus tremula</t>
+          <t>1 substratenheter # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 42239-2021 artfynd.xlsx
+++ b/artfynd/A 42239-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53973874</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53973875</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1044,8 +1059,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53973876</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>